--- a/기출문제(106~138회까지).xlsx
+++ b/기출문제(106~138회까지).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="메인표지" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="집계 및 분석" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="과년도모음" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메인표지" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="집계 및 분석" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과년도모음" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'과년도모음'!$A$1:$G$1024</definedName>
@@ -8203,7 +8203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1393"/>
+  <dimension ref="A1:P1423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col hidden="1" width="6" customWidth="1" style="2" min="1" max="1"/>
@@ -52183,6 +52183,786 @@
       <c r="G1393" s="24" t="inlineStr">
         <is>
           <t>운행중인 철도터널과 인접된 지하구조물을 설치하고자 한다. 근접시공에 따른 안전영역평가와 시공 중 보강대책을 설명하시오 .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="B1394" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1394" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>안전관리론</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>색채관리</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>1. 색채관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="B1395" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1395" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>안전관리론</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>파지와 망각</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>2. 파지와 망각</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="B1396" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1396" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>철골</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>철골건립공법</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>3. 철골건립공법</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="B1397" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1397" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>재해유형</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>밀폐공간 환기량 산정</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>4. 밀폐공간 환기량 산정</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="B1398" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1398" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>안전관리론</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>RMR(에너지 대사율)과 작업강도</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>5. RMR(에너지 대사율)과 작업강도</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="B1399" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1399" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>산안법</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>화재감시자의 배치 목적과 주요업무</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>6. 화재감시자의 배치 목적과 주요업무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="B1400" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1400" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>안전관리론</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>하세이(R.B.Hersey)의 피로원인과 대책</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>7. 하세이(R.B.Hersey)의 피로원인과 대책</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="B1401" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1401" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>건설기계</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>건설장비 사용 전 사전조사 및 작업계획서의 내용</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>8. 건설장비 사용 전 사전조사 및 작업계획서의 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="B1402" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>안전관리론</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>작업안전분석(JSA, Job Safety Analysis)의 목적과 실시 절차</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>9. 작업안전분석(JSA, Job Safety Analysis)의 목적과 실시 절차</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="B1403" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1403" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>시설물안전법</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>시설물통합정보관리시스템(FMS, Facility Management System)</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>10. 시설물통합정보관리시스템(FMS, Facility Management System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="B1404" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1404" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>건진법</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>건설기술진흥법 상 안전관리비의 항목별 산출 기준 및 주요내역</t>
+        </is>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>11. 건설기술진흥법 상 안전관리비의 항목별 산출 기준 및 주요내역</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="B1405" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1405" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>건설기계</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>펌프카를 이용하여 콘크리트 타설작업을 하는 경우 전도(넘어짐)를 예방하기 위해 필요한 안전대책</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>12. 펌프카를 이용하여 콘크리트 타설작업을 하는 경우 전도(넘어짐)를 예방하기 위해 필요한 안전대책</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="B1406" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1406" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>산안법</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>산업안전보건법령 상 휴게시설 설치, 관리 의무화 대상 사업장의 범위와 세부 설치 및 관리기준, 위반 시 과태료 부과기준</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>13. 산업안전보건법령 상 휴게시설 설치, 관리 의무화 대상 사업장의 범위와 세부 설치 및 관리기준, 위반 시 과태료 부과기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="B1407" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1407" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>안전관리론</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>자기규율 예방체계 확립을 위한 상시 위험성 평가의 주요 내용과 작업 전 안전회의(TBM)를 연계한 실행력을 강화하는 방안에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>1. 자기규율 예방체계 확립을 위한 상시 위험성 평가의 주요 내용과 작업 전 안전회의(TBM)를 연계한 실행력을 강화하는 방안에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="B1408" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1408" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>토공</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>보강토 옹벽 구성요소와 붕괴사고 원인에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>2. 보강토 옹벽 구성요소와 붕괴사고 원인에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="B1409" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1409" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>시설물안전법</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>시설물의 안전 및 유지관리에 관한 특별법 상 '안전점검 및 정밀안전진단'의 대상과 주기, 시설물의 중대한 결함 발견시 후속 조치사항에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>3. 시설물의 안전 및 유지관리에 관한 특별법 상 '안전점검 및 정밀안전진단'의 대상과 주기, 시설물의 중대한 결함 발견시 후속 조치사항에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="B1410" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1410" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>재해유형</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>고령근로자에게서 나타나는 주의와 부주의의 특징과 부주의의 발생원인 및 대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>4. 고령근로자에게서 나타나는 주의와 부주의의 특징과 부주의의 발생원인 및 대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="B1411" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1411" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>가설공사</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>건설현장에서 사용하는 강관비계와 시스템비계 조립 해체시 발생할 수 있는 재해유형과 안전대책, 각각의 설치(조립)시 준수사항에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>5. 건설현장에서 사용하는 강관비계와 시스템비계 조립 해체시 발생할 수 있는 재해유형과 안전대책, 각각의 설치(조립)시 준수사항에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="B1412" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1412" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>건설기계</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>건설현장 굴착기 작업 시 위험요인과 안전대책에 대하여 설명하고 굴착기를 사용하는 인양작업 시 준수사항에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>6. 건설현장 굴착기 작업 시 위험요인과 안전대책에 대하여 설명하고 굴착기를 사용하는 인양작업 시 준수사항에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="B1413" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1413" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>산안법</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>산업안전보건법 상 안전보건대장의 종류 및 건설공사 발주자가 단계별로 수행해야하는 업무에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>1. 산업안전보건법 상 안전보건대장의 종류 및 건설공사 발주자가 단계별로 수행해야하는 업무에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="B1414" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1414" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>건설기계</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>이동식 크레인을 사용하여 근로자를 달아 올린 상태에서 작업하는 경우 작업허용조건, 작업시 위험 요인 및 안전조치에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>2. 이동식 크레인을 사용하여 근로자를 달아 올린 상태에서 작업하는 경우 작업허용조건, 작업시 위험 요인 및 안전조치에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="B1415" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1415" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>재해유형</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>근로자 건강장해 예방프로그램의 종류와 근골격계 질환을 유발하는 부담작업의 종류 및 예방대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>4. 근로자 건강장해 예방프로그램의 종류와 근골격계 질환을 유발하는 부담작업의 종류 및 예방대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="B1416" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1416" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>토공</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>건설현장에서 굴착작업을 하는 경우 지반 종류별 굴착면의 기울기를 설명하고, 굴착작업 전 사전조사 사항과 붕괴재해 예방대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>5. 건설현장에서 굴착작업을 하는 경우 지반 종류별 굴착면의 기울기를 설명하고, 굴착작업 전 사전조사 사항과 붕괴재해 예방대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="B1417" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1417" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>산안법</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>건설업 '산업안전보건관리비 계상 및 사용기준' 에 따른 설계변경 시 산업안전보건관리비 조정 계상 방법과 관리감독자가 안전보건업무 수행 시 수당지급 작업의 종류 및 건설공사의 종류에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>6. 건설업 '산업안전보건관리비 계상 및 사용기준' 에 따른 설계변경 시 산업안전보건관리비 조정 계상 방법과 관리감독자가 안전보건업무 수행 시 수당지급 작업의 종류 및 건설공사의 종류에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="B1418" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1418" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>산안법</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>폭염 발생 시 건설현장 근로자의 '온열질환 예방을 위한 건강보호 가이드라인'과 현장의 '작업중지권'행사 등 이행력 확보 대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>1. 폭염 발생 시 건설현장 근로자의 '온열질환 예방을 위한 건강보호 가이드라인'과 현장의 '작업중지권'행사 등 이행력 확보 대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="B1419" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1419" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>안전관리론</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>안전설계기법의 종류인 페일세이프(Fail Safe)와 풀푸르푸(Fool Proof)의 특징과 건설업 적용 방안에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>2. 안전설계기법의 종류인 페일세이프(Fail Safe)와 풀푸르푸(Fool Proof)의 특징과 건설업 적용 방안에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="B1420" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1420" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>건진법</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>지하상가 건설공사 중 '건설기술진흥법'상 안전점검 종류와 실시시기 및 정기 안전점검 절차에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>3. 지하상가 건설공사 중 '건설기술진흥법'상 안전점검 종류와 실시시기 및 정기 안전점검 절차에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="B1421" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1421" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>해체공사</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>건축물 해체공사 시 공사 단계별 확인 사항과 안전관리대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>4. 건축물 해체공사 시 공사 단계별 확인 사항과 안전관리대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="B1422" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1422" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>터널</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>NATM 공법을 적용한 터널 굴착공사 중 발생하는 막장면 붕괴사고의 주요 원인을 지질학적 원인과 수문학적 원인, 그리고 시공 및 관리적 원인으로 구분하여 분석하고 붕괴사고 방지대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>5. NATM 공법을 적용한 터널 굴착공사 중 발생하는 막장면 붕괴사고의 주요 원인을 지질학적 원인과 수문학적 원인, 그리고 시공 및 관리적 원인으로 구분하여 분석하고 붕괴사고 방지대책에 대하여 설명하시오</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="B1423" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1423" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>콘크리트</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>현장배치 플랜트(Batch Plant) 설치 및 운영 시 안전관리 방안에 대하여 설명하시오</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>6. 현장배치 플랜트(Batch Plant) 설치 및 운영 시 안전관리 방안에 대하여 설명하시오</t>
         </is>
       </c>
     </row>
